--- a/cases/Case_14bus_v2/ieee14AC.xlsx
+++ b/cases/Case_14bus_v2/ieee14AC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hoss258\Projects_2324\ecomp_code_publish\ecomp-stability\SyNAPS\cases\Case_14bus_v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hoss258\Projects_2324\ecomp_code_publish\pnnl_github_version\SyNAPS\cases\Case_14bus_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFBD72B-0C4A-4423-8DF0-1914FD17E664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CA2A68-C868-49EC-A09E-2FB3EDA83CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="2865" windowWidth="21600" windowHeight="11175" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3090" windowWidth="14400" windowHeight="8175" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Toggler" sheetId="1" r:id="rId1"/>
@@ -1826,7 +1826,7 @@
         <v>138</v>
       </c>
       <c r="G9">
-        <v>0.13500000000000001</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="H9">
         <v>0.11799999999999999</v>
@@ -4471,6 +4471,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="456a9b2f-f871-4843-bba2-15044ef394ce">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="25dfa5b4-bc86-44ce-b7ec-b3aed1ad4067" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008DE0C51AA0C9134AA6CF2F5904CF542E" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dfb8ffb4bd0b5417cefca7f6c8774768">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="456a9b2f-f871-4843-bba2-15044ef394ce" xmlns:ns3="25dfa5b4-bc86-44ce-b7ec-b3aed1ad4067" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f60f0bded58eb823fefef831e68c786" ns2:_="" ns3:_="">
     <xsd:import namespace="456a9b2f-f871-4843-bba2-15044ef394ce"/>
@@ -4665,27 +4685,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF05EC7C-5C94-4981-922F-708C492DA49A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="456a9b2f-f871-4843-bba2-15044ef394ce"/>
+    <ds:schemaRef ds:uri="25dfa5b4-bc86-44ce-b7ec-b3aed1ad4067"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="456a9b2f-f871-4843-bba2-15044ef394ce">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="25dfa5b4-bc86-44ce-b7ec-b3aed1ad4067" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF3DE622-6ECD-4C2C-B369-F7F205ECE2EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB7272A7-AE5E-40CD-94CF-D29BF14F48F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4702,23 +4721,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF3DE622-6ECD-4C2C-B369-F7F205ECE2EE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF05EC7C-5C94-4981-922F-708C492DA49A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="456a9b2f-f871-4843-bba2-15044ef394ce"/>
-    <ds:schemaRef ds:uri="25dfa5b4-bc86-44ce-b7ec-b3aed1ad4067"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>